--- a/docs/paper_with_feedback/4.11shatin/test_grammar_2_['No. 91_～ば〈条件(じょうけん)〉 ']_revised - with HO's Comments.xlsx
+++ b/docs/paper_with_feedback/4.11shatin/test_grammar_2_['No. 91_～ば〈条件(じょうけん)〉 ']_revised - with HO's Comments.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14450" windowHeight="8010"/>
+    <workbookView windowWidth="23003" windowHeight="12804"/>
   </bookViews>
   <sheets>
     <sheet name="Questions" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="220">
   <si>
     <t>Question Index</t>
   </si>
@@ -5934,8 +5934,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="750570" y="39401750"/>
-        <a:ext cx="3603625" cy="2743200"/>
+        <a:off x="743585" y="37964110"/>
+        <a:ext cx="3562350" cy="2824480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5964,8 +5964,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8490585" y="37745035"/>
-        <a:ext cx="3846195" cy="2105025"/>
+        <a:off x="8344535" y="36256595"/>
+        <a:ext cx="3773170" cy="2171065"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5994,8 +5994,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="723900" y="42234485"/>
-        <a:ext cx="3603625" cy="2743200"/>
+        <a:off x="716915" y="40878125"/>
+        <a:ext cx="3562350" cy="2819400"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6024,8 +6024,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5120005" y="44121705"/>
-        <a:ext cx="5096510" cy="2743200"/>
+        <a:off x="5027295" y="42821225"/>
+        <a:ext cx="5020310" cy="2819400"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6567,20 +6567,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K134"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:K109"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="5.56363636363636" customWidth="1"/>
+    <col min="1" max="1" width="5.56481481481481" customWidth="1"/>
     <col min="2" max="2" width="32.5" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="5.23636363636364" customWidth="1"/>
-    <col min="5" max="5" width="9.40909090909091" customWidth="1"/>
-    <col min="6" max="6" width="14.6454545454545" customWidth="1"/>
-    <col min="7" max="7" width="17.9090909090909" customWidth="1"/>
-    <col min="10" max="10" width="21.6363636363636" customWidth="1"/>
+    <col min="4" max="4" width="5.24074074074074" customWidth="1"/>
+    <col min="5" max="5" width="9.40740740740741" customWidth="1"/>
+    <col min="6" max="6" width="14.6481481481481" customWidth="1"/>
+    <col min="7" max="7" width="17.9074074074074" customWidth="1"/>
+    <col min="10" max="10" width="21.6388888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="280" spans="1:7">
+    <row r="1" ht="57.6" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="42" spans="1:7">
+    <row r="2" ht="43.2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="42" spans="1:7">
+    <row r="3" ht="43.2" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="42" spans="1:7">
+    <row r="4" ht="43.2" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" ht="28" spans="1:7">
+    <row r="5" ht="28.8" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -6685,7 +6685,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" ht="42" spans="1:7">
+    <row r="6" ht="43.2" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
@@ -6704,7 +6704,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" ht="42" spans="1:7">
+    <row r="7" ht="43.2" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
@@ -6725,7 +6725,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" ht="42" spans="1:7">
+    <row r="8" ht="43.2" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
@@ -6746,7 +6746,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" ht="42" spans="1:7">
+    <row r="9" ht="43.2" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
@@ -6765,7 +6765,7 @@
       <c r="F9" s="2"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" ht="42" spans="1:7">
+    <row r="10" ht="43.2" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>39</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" ht="42" spans="1:7">
+    <row r="11" ht="43.2" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
@@ -6805,7 +6805,7 @@
       <c r="F11" s="2"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" ht="28" spans="1:7">
+    <row r="12" ht="28.8" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" ht="28" spans="1:7">
+    <row r="13" ht="28.8" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -6845,7 +6845,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" ht="28" spans="1:7">
+    <row r="14" ht="28.8" spans="1:7">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -6864,7 +6864,7 @@
       <c r="F14" s="2"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" ht="28" spans="1:7">
+    <row r="15" ht="28.8" spans="1:7">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -6883,7 +6883,7 @@
       <c r="F15" s="2"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" ht="28" spans="1:7">
+    <row r="16" ht="28.8" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -6902,7 +6902,7 @@
       <c r="F16" s="2"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" ht="28" spans="1:7">
+    <row r="17" ht="28.8" spans="1:7">
       <c r="A17" s="1" t="s">
         <v>28</v>
       </c>
@@ -6921,7 +6921,7 @@
       <c r="F17" s="2"/>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" ht="28" spans="1:7">
+    <row r="18" ht="28.8" spans="1:7">
       <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
@@ -6940,7 +6940,7 @@
       <c r="F18" s="2"/>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" ht="28" spans="1:7">
+    <row r="19" ht="28.8" spans="1:7">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -6959,7 +6959,7 @@
       <c r="F19" s="2"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" ht="28" spans="1:7">
+    <row r="20" ht="28.8" spans="1:7">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -6978,7 +6978,7 @@
       <c r="F20" s="2"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" ht="28" spans="1:7">
+    <row r="21" ht="28.8" spans="1:7">
       <c r="A21" s="1" t="s">
         <v>44</v>
       </c>
@@ -6997,7 +6997,7 @@
       <c r="F21" s="2"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" ht="28" spans="1:7">
+    <row r="22" ht="28.8" spans="1:7">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" ht="28" spans="1:7">
+    <row r="23" ht="28.8" spans="1:7">
       <c r="A23" s="1" t="s">
         <v>13</v>
       </c>
@@ -7037,7 +7037,7 @@
       <c r="F23" s="2"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" ht="28" spans="1:7">
+    <row r="24" ht="28.8" spans="1:7">
       <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
@@ -7058,7 +7058,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" ht="28" spans="1:7">
+    <row r="25" ht="28.8" spans="1:7">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" ht="28" spans="1:7">
+    <row r="26" ht="28.8" spans="1:7">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" ht="28" spans="1:7">
+    <row r="27" ht="28.8" spans="1:7">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -7121,7 +7121,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" ht="28" spans="1:7">
+    <row r="28" ht="28.8" spans="1:7">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
@@ -7142,7 +7142,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" ht="28" spans="1:7">
+    <row r="29" ht="28.8" spans="1:7">
       <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
@@ -7163,7 +7163,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="30" ht="28" spans="1:7">
+    <row r="30" ht="28.8" spans="1:7">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
@@ -7182,7 +7182,7 @@
       <c r="F30" s="2"/>
       <c r="G30" s="4"/>
     </row>
-    <row r="31" ht="28" spans="1:7">
+    <row r="31" ht="28.8" spans="1:7">
       <c r="A31" s="1" t="s">
         <v>44</v>
       </c>
@@ -7201,7 +7201,7 @@
       <c r="F31" s="2"/>
       <c r="G31" s="4"/>
     </row>
-    <row r="32" ht="28" spans="1:7">
+    <row r="32" ht="28.8" spans="1:7">
       <c r="A32" s="1" t="s">
         <v>7</v>
       </c>
@@ -7222,7 +7222,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" ht="28" spans="1:7">
+    <row r="33" ht="28.8" spans="1:7">
       <c r="A33" s="1" t="s">
         <v>13</v>
       </c>
@@ -7241,7 +7241,7 @@
       <c r="F33" s="2"/>
       <c r="G33" s="4"/>
     </row>
-    <row r="34" ht="42" spans="1:7">
+    <row r="34" ht="43.2" spans="1:7">
       <c r="A34" s="1" t="s">
         <v>17</v>
       </c>
@@ -7260,7 +7260,7 @@
       <c r="F34" s="2"/>
       <c r="G34" s="4"/>
     </row>
-    <row r="35" ht="42" spans="1:7">
+    <row r="35" ht="43.2" spans="1:7">
       <c r="A35" s="1" t="s">
         <v>21</v>
       </c>
@@ -7281,7 +7281,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="36" ht="28" spans="1:7">
+    <row r="36" ht="28.8" spans="1:7">
       <c r="A36" s="1" t="s">
         <v>25</v>
       </c>
@@ -7300,7 +7300,7 @@
       <c r="F36" s="2"/>
       <c r="G36" s="4"/>
     </row>
-    <row r="37" ht="42" spans="1:7">
+    <row r="37" ht="43.2" spans="1:7">
       <c r="A37" s="1" t="s">
         <v>28</v>
       </c>
@@ -7319,7 +7319,7 @@
       <c r="F37" s="2"/>
       <c r="G37" s="4"/>
     </row>
-    <row r="38" ht="42" spans="1:7">
+    <row r="38" ht="43.2" spans="1:7">
       <c r="A38" s="1" t="s">
         <v>32</v>
       </c>
@@ -7338,7 +7338,7 @@
       <c r="F38" s="2"/>
       <c r="G38" s="4"/>
     </row>
-    <row r="39" ht="28" spans="1:7">
+    <row r="39" ht="28.8" spans="1:7">
       <c r="A39" s="1" t="s">
         <v>36</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="40" ht="28" spans="1:7">
+    <row r="40" ht="28.8" spans="1:7">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -7378,7 +7378,7 @@
       <c r="F40" s="2"/>
       <c r="G40" s="4"/>
     </row>
-    <row r="41" ht="28" spans="1:7">
+    <row r="41" ht="28.8" spans="1:7">
       <c r="A41" s="1" t="s">
         <v>44</v>
       </c>
@@ -7397,7 +7397,7 @@
       <c r="F41" s="2"/>
       <c r="G41" s="4"/>
     </row>
-    <row r="42" ht="28" spans="1:7">
+    <row r="42" ht="28.8" spans="1:7">
       <c r="A42" s="5" t="s">
         <v>7</v>
       </c>
@@ -7418,7 +7418,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="43" ht="28" spans="1:7">
+    <row r="43" ht="28.8" spans="1:7">
       <c r="A43" s="5" t="s">
         <v>13</v>
       </c>
@@ -7437,7 +7437,7 @@
       <c r="F43" s="2"/>
       <c r="G43" s="4"/>
     </row>
-    <row r="44" ht="28" spans="1:7">
+    <row r="44" ht="28.8" spans="1:7">
       <c r="A44" s="5" t="s">
         <v>17</v>
       </c>
@@ -7456,7 +7456,7 @@
       <c r="F44" s="2"/>
       <c r="G44" s="4"/>
     </row>
-    <row r="45" ht="28" spans="1:7">
+    <row r="45" ht="28.8" spans="1:7">
       <c r="A45" s="5" t="s">
         <v>21</v>
       </c>
@@ -7475,7 +7475,7 @@
       <c r="F45" s="2"/>
       <c r="G45" s="4"/>
     </row>
-    <row r="46" ht="28" spans="1:7">
+    <row r="46" ht="28.8" spans="1:7">
       <c r="A46" s="5" t="s">
         <v>25</v>
       </c>
@@ -7494,7 +7494,7 @@
       <c r="F46" s="2"/>
       <c r="G46" s="4"/>
     </row>
-    <row r="47" ht="28" spans="1:7">
+    <row r="47" ht="28.8" spans="1:7">
       <c r="A47" s="5" t="s">
         <v>28</v>
       </c>
@@ -7513,7 +7513,7 @@
       <c r="F47" s="2"/>
       <c r="G47" s="4"/>
     </row>
-    <row r="48" ht="28" spans="1:7">
+    <row r="48" ht="28.8" spans="1:7">
       <c r="A48" s="5" t="s">
         <v>32</v>
       </c>
@@ -7532,7 +7532,7 @@
       <c r="F48" s="2"/>
       <c r="G48" s="4"/>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" ht="28.8" spans="1:7">
       <c r="A49" s="5" t="s">
         <v>36</v>
       </c>
@@ -7551,7 +7551,7 @@
       <c r="F49" s="2"/>
       <c r="G49" s="4"/>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" ht="28.8" spans="1:7">
       <c r="A50" s="5" t="s">
         <v>39</v>
       </c>
@@ -7570,7 +7570,7 @@
       <c r="F50" s="2"/>
       <c r="G50" s="4"/>
     </row>
-    <row r="51" ht="28" spans="1:7">
+    <row r="51" ht="28.8" spans="1:7">
       <c r="A51" s="5" t="s">
         <v>44</v>
       </c>
@@ -7589,7 +7589,7 @@
       <c r="F51" s="2"/>
       <c r="G51" s="4"/>
     </row>
-    <row r="52" ht="42" spans="1:7">
+    <row r="52" ht="43.2" spans="1:7">
       <c r="A52" s="1" t="s">
         <v>7</v>
       </c>
@@ -7610,7 +7610,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="53" ht="56" spans="1:7">
+    <row r="53" ht="57.6" spans="1:7">
       <c r="A53" s="1" t="s">
         <v>13</v>
       </c>
@@ -7629,7 +7629,7 @@
       <c r="F53" s="2"/>
       <c r="G53" s="4"/>
     </row>
-    <row r="54" ht="56" spans="1:7">
+    <row r="54" ht="57.6" spans="1:7">
       <c r="A54" s="1" t="s">
         <v>17</v>
       </c>
@@ -7648,7 +7648,7 @@
       <c r="F54" s="2"/>
       <c r="G54" s="4"/>
     </row>
-    <row r="55" ht="42" spans="1:7">
+    <row r="55" ht="43.2" spans="1:7">
       <c r="A55" s="1" t="s">
         <v>21</v>
       </c>
@@ -7667,7 +7667,7 @@
       <c r="F55" s="2"/>
       <c r="G55" s="4"/>
     </row>
-    <row r="56" ht="56" spans="1:7">
+    <row r="56" ht="57.6" spans="1:7">
       <c r="A56" s="1" t="s">
         <v>25</v>
       </c>
@@ -7686,7 +7686,7 @@
       <c r="F56" s="2"/>
       <c r="G56" s="4"/>
     </row>
-    <row r="57" ht="42" spans="1:7">
+    <row r="57" ht="43.2" spans="1:7">
       <c r="A57" s="1" t="s">
         <v>28</v>
       </c>
@@ -7705,7 +7705,7 @@
       <c r="F57" s="2"/>
       <c r="G57" s="4"/>
     </row>
-    <row r="58" ht="56" spans="1:7">
+    <row r="58" ht="57.6" spans="1:7">
       <c r="A58" s="1" t="s">
         <v>32</v>
       </c>
@@ -7724,7 +7724,7 @@
       <c r="F58" s="2"/>
       <c r="G58" s="4"/>
     </row>
-    <row r="59" ht="56" spans="1:7">
+    <row r="59" ht="57.6" spans="1:7">
       <c r="A59" s="1" t="s">
         <v>36</v>
       </c>
@@ -7743,7 +7743,7 @@
       <c r="F59" s="2"/>
       <c r="G59" s="4"/>
     </row>
-    <row r="60" ht="42" spans="1:7">
+    <row r="60" ht="43.2" spans="1:7">
       <c r="A60" s="1" t="s">
         <v>39</v>
       </c>
@@ -7762,7 +7762,7 @@
       <c r="F60" s="2"/>
       <c r="G60" s="4"/>
     </row>
-    <row r="61" ht="70" spans="1:7">
+    <row r="61" ht="72" spans="1:7">
       <c r="A61" s="1" t="s">
         <v>44</v>
       </c>
@@ -7781,7 +7781,7 @@
       <c r="F61" s="2"/>
       <c r="G61" s="4"/>
     </row>
-    <row r="62" ht="28" spans="1:7">
+    <row r="62" ht="28.8" spans="1:7">
       <c r="A62" s="1" t="s">
         <v>7</v>
       </c>
@@ -7800,7 +7800,7 @@
       <c r="F62" s="2"/>
       <c r="G62" s="4"/>
     </row>
-    <row r="63" ht="42" spans="1:7">
+    <row r="63" ht="43.2" spans="1:7">
       <c r="A63" s="1" t="s">
         <v>13</v>
       </c>
@@ -7819,7 +7819,7 @@
       <c r="F63" s="2"/>
       <c r="G63" s="4"/>
     </row>
-    <row r="64" ht="28" spans="1:7">
+    <row r="64" ht="28.8" spans="1:7">
       <c r="A64" s="1" t="s">
         <v>17</v>
       </c>
@@ -7838,7 +7838,7 @@
       <c r="F64" s="2"/>
       <c r="G64" s="4"/>
     </row>
-    <row r="65" ht="42" spans="1:7">
+    <row r="65" ht="43.2" spans="1:7">
       <c r="A65" s="1" t="s">
         <v>21</v>
       </c>
@@ -7857,7 +7857,7 @@
       <c r="F65" s="2"/>
       <c r="G65" s="4"/>
     </row>
-    <row r="66" ht="56" spans="1:7">
+    <row r="66" ht="57.6" spans="1:7">
       <c r="A66" s="1" t="s">
         <v>25</v>
       </c>
@@ -7876,7 +7876,7 @@
       <c r="F66" s="2"/>
       <c r="G66" s="4"/>
     </row>
-    <row r="67" ht="42" spans="1:7">
+    <row r="67" ht="43.2" spans="1:7">
       <c r="A67" s="1" t="s">
         <v>28</v>
       </c>
@@ -7895,7 +7895,7 @@
       <c r="F67" s="2"/>
       <c r="G67" s="4"/>
     </row>
-    <row r="68" ht="56" spans="1:7">
+    <row r="68" ht="57.6" spans="1:7">
       <c r="A68" s="1" t="s">
         <v>32</v>
       </c>
@@ -7914,7 +7914,7 @@
       <c r="F68" s="2"/>
       <c r="G68" s="4"/>
     </row>
-    <row r="69" ht="42" spans="1:7">
+    <row r="69" ht="43.2" spans="1:7">
       <c r="A69" s="1" t="s">
         <v>36</v>
       </c>
@@ -7933,7 +7933,7 @@
       <c r="F69" s="2"/>
       <c r="G69" s="4"/>
     </row>
-    <row r="70" ht="56" spans="1:7">
+    <row r="70" ht="57.6" spans="1:7">
       <c r="A70" s="1" t="s">
         <v>39</v>
       </c>
@@ -7952,7 +7952,7 @@
       <c r="F70" s="2"/>
       <c r="G70" s="4"/>
     </row>
-    <row r="71" ht="42" spans="1:7">
+    <row r="71" ht="43.2" spans="1:7">
       <c r="A71" s="1" t="s">
         <v>44</v>
       </c>
@@ -7971,7 +7971,7 @@
       <c r="F71" s="2"/>
       <c r="G71" s="4"/>
     </row>
-    <row r="72" ht="28" spans="1:7">
+    <row r="72" ht="28.8" spans="1:7">
       <c r="A72" s="1" t="s">
         <v>7</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="73" ht="28" spans="1:7">
+    <row r="73" ht="28.8" spans="1:7">
       <c r="A73" s="1" t="s">
         <v>13</v>
       </c>
@@ -8013,7 +8013,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="74" ht="28" spans="1:7">
+    <row r="74" ht="28.8" spans="1:7">
       <c r="A74" s="1" t="s">
         <v>17</v>
       </c>
@@ -8034,7 +8034,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="75" ht="28" spans="1:7">
+    <row r="75" ht="28.8" spans="1:7">
       <c r="A75" s="1" t="s">
         <v>21</v>
       </c>
@@ -8055,7 +8055,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="76" ht="28" spans="1:7">
+    <row r="76" ht="28.8" spans="1:7">
       <c r="A76" s="1" t="s">
         <v>25</v>
       </c>
@@ -8076,7 +8076,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="77" ht="28" spans="1:7">
+    <row r="77" ht="28.8" spans="1:7">
       <c r="A77" s="1" t="s">
         <v>28</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="78" ht="28" spans="1:7">
+    <row r="78" ht="28.8" spans="1:7">
       <c r="A78" s="1" t="s">
         <v>32</v>
       </c>
@@ -8118,7 +8118,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="79" ht="28" spans="1:7">
+    <row r="79" ht="28.8" spans="1:7">
       <c r="A79" s="1" t="s">
         <v>36</v>
       </c>
@@ -8139,7 +8139,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="80" ht="28" spans="1:7">
+    <row r="80" ht="28.8" spans="1:7">
       <c r="A80" s="1" t="s">
         <v>39</v>
       </c>
@@ -8160,7 +8160,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="81" ht="28" spans="1:7">
+    <row r="81" ht="28.8" spans="1:7">
       <c r="A81" s="1" t="s">
         <v>44</v>
       </c>
@@ -8556,107 +8556,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" ht="280" spans="1:6">
-      <c r="A130" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="131" ht="42" spans="1:6">
-      <c r="A131" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="132" ht="42" spans="1:6">
-      <c r="A132" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="133" ht="42" spans="1:6">
-      <c r="A133" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F133" s="4"/>
-    </row>
-    <row r="134" ht="42" spans="1:6">
-      <c r="A134" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="E2:E33 E35:E81 E131:E134">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E33 E35:E81">
       <formula1>"High_Q,Low_Q,Drop,Minor changes"</formula1>
     </dataValidation>
   </dataValidations>
